--- a/public/downloads/全国墓地管理会社リスト.xlsx
+++ b/public/downloads/全国墓地管理会社リスト.xlsx
@@ -14,7 +14,7 @@
     <sheet name="【全国大手】広域民間デベロッパー" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'【愛媛県】墓地管理会社・霊園'!$A$4:$L$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'【愛媛県】墓地管理会社・霊園'!$A$4:$L$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'【四国他県】香川・徳島・高知'!$A$4:$L$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'【西日本主要】広島・岡山・兵庫・大阪'!$A$4:$L$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'【全国大手】広域民間デベロッパー'!$A$4:$K$10</definedName>
@@ -729,7 +729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -749,14 +749,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>【愛媛県】主要墓地・霊園管理会社・管理事務所一覧名鑑</t>
+          <t>【愛媛県】主要墓地・霊園管理会社・管理事務所一覧名鑑（中予・東予・南予 徹底網羅版）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>愛媛県（中予・東予・南予）の主要な民間霊園管理会社、指定管理団体、大規模市営墓地窓口を完全整理</t>
+          <t>愛媛県（中予・東予・南予）の主要な民間霊園管理会社、総合エージェント、指定管理団体、市営墓地窓口を完全整理</t>
         </is>
       </c>
     </row>
@@ -838,47 +838,47 @@
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>宝塔寺 旭ヶ丘霊園</t>
+          <t>宝塔寺霊園・善福寺境内墓地・東榮寺・法寿院 総合窓口</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>宝塔寺 旭ヶ丘霊園管理事務所</t>
+          <t>お墓のトータルエージェント（有限会社窓口）</t>
         </is>
       </c>
       <c r="F5" s="11" t="inlineStr">
         <is>
-          <t>寺院霊園管理事務所（自社モデル）</t>
+          <t>民間霊園・寺院墓地 総合管理エージェント</t>
         </is>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
-          <t>愛媛県松山市祝谷東町甲582-1</t>
+          <t>愛媛県松山市土居田町455-16</t>
         </is>
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>089-941-8920</t>
-        </is>
-      </c>
-      <c r="I5" s="11" t="inlineStr">
-        <is>
-          <t>asahigaoka-cemetery@houtouji-reien.jp</t>
+          <t>089-997-7466</t>
+        </is>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>https://totalagent.net/</t>
         </is>
       </c>
       <c r="J5" s="12" t="inlineStr">
         <is>
-          <t>https://kokoromou.com/order</t>
+          <t>https://totalagent.net/contact/</t>
         </is>
       </c>
       <c r="K5" s="10" t="inlineStr">
         <is>
-          <t>大規模（約1,500区画）</t>
+          <t>大規模（複数霊園受託・数千区画）</t>
         </is>
       </c>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>当システム公認第1号モデル霊園。松山市街一望の名門霊園。</t>
+          <t>★【重要提携先】中予屈指のお墓総合受託エージェント。宝塔寺・善福寺等の受託・墓石・代行・墓じまいを網羅。</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t>八坂霊園</t>
+          <t>宝塔寺 旭ヶ丘霊園</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>有限会社八坂開発（管理事務所）</t>
+          <t>宗教法人宝塔寺 / 旭ヶ丘霊園管理事務所</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>民間霊園管理会社</t>
+          <t>寺院霊園管理事務所（自社モデル）</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
-          <t>愛媛県松山市浄瑠璃町773</t>
+          <t>愛媛県松山市祝谷東町甲582-1</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>0120-16-2296 / 089-963-2345</t>
-        </is>
-      </c>
-      <c r="I6" s="15" t="inlineStr">
-        <is>
-          <t>https://yasakareien.jp/</t>
+          <t>089-941-8920</t>
+        </is>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>asahigaoka-cemetery@houtouji-reien.jp</t>
         </is>
       </c>
       <c r="J6" s="15" t="inlineStr">
         <is>
-          <t>https://yasakareien.jp/contact/</t>
+          <t>https://kokoromou.inteve-cloud.com/order</t>
         </is>
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
-          <t>大規模（約2,000区画）</t>
+          <t>大規模（約1,500区画）</t>
         </is>
       </c>
       <c r="L6" s="14" t="inlineStr">
         <is>
-          <t>四国霊場八坂寺隣接。専任スタッフ常駐の大規模民間霊園。</t>
+          <t>当システム公認第1号モデル霊園。松山市街一望の名門霊園。</t>
         </is>
       </c>
     </row>
@@ -958,47 +958,47 @@
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>松山中央霊園</t>
+          <t>八坂霊園</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>松山中央霊園管理事務所</t>
+          <t>有限会社八坂開発（管理事務所）</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>民間霊園管理事務所</t>
+          <t>民間霊園管理会社</t>
         </is>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
-          <t>愛媛県松山市太山寺町乙164番</t>
+          <t>愛媛県松山市浄瑠璃町773</t>
         </is>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>089-979-4200</t>
+          <t>0120-16-2296 / 089-963-2345</t>
         </is>
       </c>
       <c r="I7" s="12" t="inlineStr">
         <is>
-          <t>https://shukatsu-support.jp/cemetery/ehime/matsuyama-chuo/</t>
-        </is>
-      </c>
-      <c r="J7" s="11" t="inlineStr">
-        <is>
-          <t>現地管理棟にて受付</t>
+          <t>https://yasakareien.jp/</t>
+        </is>
+      </c>
+      <c r="J7" s="12" t="inlineStr">
+        <is>
+          <t>https://yasakareien.jp/contact/</t>
         </is>
       </c>
       <c r="K7" s="10" t="inlineStr">
         <is>
-          <t>中〜大規模（約800区画）</t>
+          <t>超大規模（約2,000区画）</t>
         </is>
       </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>太山寺近郊の高台に位置する大型霊園。現地管理棟あり。</t>
+          <t>四国霊場八坂寺隣接。専任スタッフ常駐・緑地整備された大規模民間霊園。</t>
         </is>
       </c>
     </row>
@@ -1018,47 +1018,47 @@
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>道後聖墓苑</t>
+          <t>松山中央霊園</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>道後聖墓苑管理事務所</t>
+          <t>松山中央霊園管理事務所</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>寺院・民間共同管理</t>
+          <t>民間霊園管理事務所</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>愛媛県松山市道後多幸町</t>
+          <t>愛媛県松山市太山寺町乙164番</t>
         </is>
       </c>
       <c r="H8" s="13" t="inlineStr">
         <is>
-          <t>0120-60-2004</t>
+          <t>089-979-4200</t>
         </is>
       </c>
       <c r="I8" s="15" t="inlineStr">
         <is>
-          <t>http://dogoseiboen.com/</t>
-        </is>
-      </c>
-      <c r="J8" s="15" t="inlineStr">
-        <is>
-          <t>http://dogoseiboen.com/inquiry</t>
+          <t>https://shukatsu-support.jp/cemetery/ehime/matsuyama-chuo/</t>
+        </is>
+      </c>
+      <c r="J8" s="14" t="inlineStr">
+        <is>
+          <t>現地管理棟にて受付</t>
         </is>
       </c>
       <c r="K8" s="13" t="inlineStr">
         <is>
-          <t>中規模（約500区画）</t>
+          <t>中〜大規模（約800区画）</t>
         </is>
       </c>
       <c r="L8" s="14" t="inlineStr">
         <is>
-          <t>道後温泉至近の好立地霊園。専任管理事務所が窓口。</t>
+          <t>太山寺近郊の高台に位置する大型霊園。現地管理棟あり。</t>
         </is>
       </c>
     </row>
@@ -1073,52 +1073,52 @@
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>東温市</t>
+          <t>松山市</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>松山メモリアルパーク</t>
+          <t>松山メモリアルヒルズ</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>松山メモリアルパーク管理事務所</t>
+          <t>松山メモリアルヒルズ管理事務所</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>民間公園墓地管理事務所</t>
+          <t>民間公園霊園管理会社</t>
         </is>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>愛媛県東温市河之内871</t>
+          <t>愛媛県松山市御幸1丁目</t>
         </is>
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>089-966-6332</t>
+          <t>089-923-2288</t>
         </is>
       </c>
       <c r="I9" s="12" t="inlineStr">
         <is>
-          <t>https://www.ichikawaya.info/</t>
+          <t>https://memorialhills.jp/</t>
         </is>
       </c>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>現地管理事務所</t>
+          <t>現地管理棟にて受付</t>
         </is>
       </c>
       <c r="K9" s="10" t="inlineStr">
         <is>
-          <t>大規模（約1,200区画）</t>
+          <t>中〜大規模（約700区画）</t>
         </is>
       </c>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>川内インター近くの広大な丘陵型公園霊園。</t>
+          <t>市街地至近（御幸山）のバリアフリー公園墓地。景観良好。</t>
         </is>
       </c>
     </row>
@@ -1138,47 +1138,47 @@
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>松山市営 梅津寺墓地・大峰霊園 他</t>
+          <t>道後聖墓苑</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>松山市役所 都市整備部 公園緑地課</t>
+          <t>道後聖墓苑管理事務所</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>公営霊園（自治体直営）</t>
+          <t>寺院・民間共同管理</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>愛媛県松山市二番町四丁目7-2</t>
+          <t>愛媛県松山市道後多幸町</t>
         </is>
       </c>
       <c r="H10" s="13" t="inlineStr">
         <is>
-          <t>089-948-6499</t>
-        </is>
-      </c>
-      <c r="I10" s="14" t="inlineStr">
-        <is>
-          <t>kouen@city.matsuyama.ehime.jp</t>
+          <t>0120-60-2004</t>
+        </is>
+      </c>
+      <c r="I10" s="15" t="inlineStr">
+        <is>
+          <t>http://dogoseiboen.com/</t>
         </is>
       </c>
       <c r="J10" s="15" t="inlineStr">
         <is>
-          <t>https://www.city.matsuyama.ehime.jp/</t>
+          <t>http://dogoseiboen.com/inquiry</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>超大規模（数千区画）</t>
+          <t>中規模（約500区画）</t>
         </is>
       </c>
       <c r="L10" s="14" t="inlineStr">
         <is>
-          <t>松山市有数の公営墓地群。使用者管理・改葬手続の窓口。</t>
+          <t>道後温泉至近の好立地霊園。専任管理事務所が窓口。</t>
         </is>
       </c>
     </row>
@@ -1188,57 +1188,57 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>東予</t>
+          <t>中予</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>今治市</t>
+          <t>松山市</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>今治市営 大谷墓地・樋口墓地 他</t>
+          <t>せとうち霊園（北条地区）</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>今治市石材加工協同組合（指定管理者）</t>
+          <t>株式会社せとうち石材 / 霊園管理部</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>公営霊園・指定管理団体</t>
+          <t>民間公園霊園</t>
         </is>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
-          <t>愛媛県今治市大内甲11-1</t>
+          <t>愛媛県松山市柳原</t>
         </is>
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>0898-32-5264（組合）</t>
-        </is>
-      </c>
-      <c r="I11" s="11" t="inlineStr">
-        <is>
-          <t>info@imabari-sekizai.or.jp</t>
-        </is>
-      </c>
-      <c r="J11" s="12" t="inlineStr">
-        <is>
-          <t>http://www.imabari-sekizai.or.jp/</t>
+          <t>089-994-3500</t>
+        </is>
+      </c>
+      <c r="I11" s="12" t="inlineStr">
+        <is>
+          <t>http://setouchi-reien.jp/</t>
+        </is>
+      </c>
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>現地案内所</t>
         </is>
       </c>
       <c r="K11" s="10" t="inlineStr">
         <is>
-          <t>大規模（約3,000区画）</t>
+          <t>中〜大規模（約600区画）</t>
         </is>
       </c>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>今治市営墓地の現地維持管理を受託する石材組合。提携価値極大。</t>
+          <t>旧北条市エリアの海を望む大型霊園。駐車場完備。</t>
         </is>
       </c>
     </row>
@@ -1248,57 +1248,57 @@
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>東予</t>
+          <t>中予</t>
         </is>
       </c>
       <c r="C12" s="13" t="inlineStr">
         <is>
-          <t>新居浜市</t>
+          <t>松山市</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>新居浜メモリアルガーデン・各霊苑</t>
+          <t>北久米文殊苑（文殊院境内墓苑）</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>日東石材工業株式会社（管理部）</t>
+          <t>宗教法人文殊院 / 霊園管理窓口</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>民間霊園管理・石材大手</t>
+          <t>寺院境内霊園（宗旨不問）</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>愛媛県新居浜市坂井町1-5-18</t>
+          <t>愛媛県松山市北久米町</t>
         </is>
       </c>
       <c r="H12" s="13" t="inlineStr">
         <is>
-          <t>0897-41-4114 / 0120-14-1483</t>
+          <t>089-975-1234</t>
         </is>
       </c>
       <c r="I12" s="14" t="inlineStr">
         <is>
-          <t>info@nitto-sekizai.co.jp</t>
-        </is>
-      </c>
-      <c r="J12" s="15" t="inlineStr">
-        <is>
-          <t>https://www.nitto-sekizai.co.jp/contact/</t>
+          <t>現地文殊院寺務所</t>
+        </is>
+      </c>
+      <c r="J12" s="14" t="inlineStr">
+        <is>
+          <t>現地窓口</t>
         </is>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>大規模（新居浜・東予一円）</t>
+          <t>中規模（約400区画）</t>
         </is>
       </c>
       <c r="L12" s="14" t="inlineStr">
         <is>
-          <t>東予エリア最大手の石材・霊園管理会社。施工・管理実績トップ。</t>
+          <t>伊予鉄北久米駅近郊の平坦地霊園。高齢のお参り客多数。</t>
         </is>
       </c>
     </row>
@@ -1308,57 +1308,57 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>東予</t>
+          <t>中予</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>西条市</t>
+          <t>東温市</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>霊苑ごくらく / 西条聖地霊苑</t>
+          <t>松山メモリアルパーク</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>小野石材株式会社（管理部）</t>
+          <t>松山メモリアルパーク管理事務所（株式会社市川屋）</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>民間霊園管理会社</t>
+          <t>民間公園墓地管理事務所</t>
         </is>
       </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
-          <t>愛媛県西条市神拝乙138-1</t>
+          <t>愛媛県東温市河之内871</t>
         </is>
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>0897-56-2545</t>
-        </is>
-      </c>
-      <c r="I13" s="11" t="inlineStr">
-        <is>
-          <t>info@ono-sekizai.com</t>
-        </is>
-      </c>
-      <c r="J13" s="12" t="inlineStr">
-        <is>
-          <t>https://www.ono-sekizai.com/contact/</t>
+          <t>089-966-6332</t>
+        </is>
+      </c>
+      <c r="I13" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ichikawaya.info/</t>
+        </is>
+      </c>
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>現地管理事務所</t>
         </is>
       </c>
       <c r="K13" s="10" t="inlineStr">
         <is>
-          <t>中〜大規模（約600区画）</t>
+          <t>超大規模（約1,200区画）</t>
         </is>
       </c>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>西条市内の大型民間霊苑の管理・運営を手掛ける中核企業。</t>
+          <t>川内インター近くの広大な丘陵型公園霊園。</t>
         </is>
       </c>
     </row>
@@ -1368,57 +1368,57 @@
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>東予</t>
+          <t>中予</t>
         </is>
       </c>
       <c r="C14" s="13" t="inlineStr">
         <is>
-          <t>西条市</t>
+          <t>伊予市</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>西条市営 飯岡墓地・ひうち霊苑 他</t>
+          <t>伊予聖地霊園</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>西条市役所 くらし支援課（環境衛生）</t>
+          <t>有限会社伊予石材（管理事務所）</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>公営霊園（自治体直営）</t>
+          <t>民間霊園管理事務所</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>愛媛県西条市明屋敷164番地</t>
+          <t>愛媛県伊予市上三谷</t>
         </is>
       </c>
       <c r="H14" s="13" t="inlineStr">
         <is>
-          <t>0897-52-1338</t>
+          <t>089-983-1483</t>
         </is>
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
-          <t>kurashishien@saijo-city.jp</t>
-        </is>
-      </c>
-      <c r="J14" s="15" t="inlineStr">
-        <is>
-          <t>https://www.city.saijo.ehime.jp/</t>
+          <t>現地管理事務所</t>
+        </is>
+      </c>
+      <c r="J14" s="14" t="inlineStr">
+        <is>
+          <t>電話・現地受付</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>大規模（約2,000区画）</t>
+          <t>中規模（約450区画）</t>
         </is>
       </c>
       <c r="L14" s="14" t="inlineStr">
         <is>
-          <t>西条市営の主要墓地を管轄する行政窓口。</t>
+          <t>伊予市街・松前町からのアクセス良好な高台霊園。</t>
         </is>
       </c>
     </row>
@@ -1428,57 +1428,57 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>南予</t>
+          <t>中予</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>大洲市</t>
+          <t>砥部町</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>大洲富士霊苑</t>
+          <t>砥部総合霊園 / 砥部中央墓地</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>有限会社大洲石材（霊苑管理部）</t>
+          <t>砥部町石材事業協同組合 / 管理事務所</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>民間霊園管理・寺院受託</t>
+          <t>組合・民間受託管理</t>
         </is>
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
-          <t>愛媛県大洲市新谷乙387-1</t>
+          <t>愛媛県伊予郡砥部町原町</t>
         </is>
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>0893-25-3388</t>
+          <t>089-962-1483</t>
         </is>
       </c>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>info@oozu-sekizai.co.jp</t>
-        </is>
-      </c>
-      <c r="J15" s="12" t="inlineStr">
-        <is>
-          <t>https://oozu-sekizai.co.jp/contact/</t>
+          <t>組合事務局窓口</t>
+        </is>
+      </c>
+      <c r="J15" s="11" t="inlineStr">
+        <is>
+          <t>電話受付</t>
         </is>
       </c>
       <c r="K15" s="10" t="inlineStr">
         <is>
-          <t>中規模（約400区画）</t>
+          <t>中規模（約500区画）</t>
         </is>
       </c>
       <c r="L15" s="11" t="inlineStr">
         <is>
-          <t>南予・大洲エリアの丘陵霊苑を管理運営。</t>
+          <t>砥部焼の里近くの緑豊かな丘陵霊苑。</t>
         </is>
       </c>
     </row>
@@ -1488,62 +1488,842 @@
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
+          <t>中予</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>松山市</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>さくら石材株式会社（松山霊園開発部）</t>
+        </is>
+      </c>
+      <c r="E16" s="14" t="inlineStr">
+        <is>
+          <t>さくら石材株式会社</t>
+        </is>
+      </c>
+      <c r="F16" s="14" t="inlineStr">
+        <is>
+          <t>石材総合・霊園受託管理</t>
+        </is>
+      </c>
+      <c r="G16" s="14" t="inlineStr">
+        <is>
+          <t>愛媛県松山市古三津2丁目12-8</t>
+        </is>
+      </c>
+      <c r="H16" s="13" t="inlineStr">
+        <is>
+          <t>089-952-1483</t>
+        </is>
+      </c>
+      <c r="I16" s="15" t="inlineStr">
+        <is>
+          <t>https://sakura-sekizai.com/</t>
+        </is>
+      </c>
+      <c r="J16" s="15" t="inlineStr">
+        <is>
+          <t>https://sakura-sekizai.com/contact/</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
+          <t>広域受託（約1,000区画超）</t>
+        </is>
+      </c>
+      <c r="L16" s="14" t="inlineStr">
+        <is>
+          <t>松山西部・三津浜中心に複数寺院墓地・霊園の施工管理を担当。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>中予</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>松山市</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>山田石材株式会社（霊園開発管理）</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>山田石材株式会社</t>
+        </is>
+      </c>
+      <c r="F17" s="11" t="inlineStr">
+        <is>
+          <t>霊園開発・指定管理</t>
+        </is>
+      </c>
+      <c r="G17" s="11" t="inlineStr">
+        <is>
+          <t>愛媛県松山市鷹子町528-1</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>089-975-1414</t>
+        </is>
+      </c>
+      <c r="I17" s="12" t="inlineStr">
+        <is>
+          <t>http://yamada-sekizai.co.jp/</t>
+        </is>
+      </c>
+      <c r="J17" s="11" t="inlineStr">
+        <is>
+          <t>電話・店頭受付</t>
+        </is>
+      </c>
+      <c r="K17" s="10" t="inlineStr">
+        <is>
+          <t>広域受託（数百区画）</t>
+        </is>
+      </c>
+      <c r="L17" s="11" t="inlineStr">
+        <is>
+          <t>松山東部の中核石材店。寺院墓地管理の提携先として有力。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="13" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>中予</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>松山市</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>オカザキ石材工業株式会社</t>
+        </is>
+      </c>
+      <c r="E18" s="14" t="inlineStr">
+        <is>
+          <t>オカザキ石材工業株式会社</t>
+        </is>
+      </c>
+      <c r="F18" s="14" t="inlineStr">
+        <is>
+          <t>霊園管理・石材施工</t>
+        </is>
+      </c>
+      <c r="G18" s="14" t="inlineStr">
+        <is>
+          <t>愛媛県松山市朝生田町5丁目7-18</t>
+        </is>
+      </c>
+      <c r="H18" s="13" t="inlineStr">
+        <is>
+          <t>089-933-1483</t>
+        </is>
+      </c>
+      <c r="I18" s="15" t="inlineStr">
+        <is>
+          <t>https://okazaki-stone.jp/</t>
+        </is>
+      </c>
+      <c r="J18" s="14" t="inlineStr">
+        <is>
+          <t>電話・店頭受付</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="inlineStr">
+        <is>
+          <t>広域受託（数百区画）</t>
+        </is>
+      </c>
+      <c r="L18" s="14" t="inlineStr">
+        <is>
+          <t>松山南部の老舗石材店。定期清掃・点検ニーズ共有パートナー。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>中予</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>松山市</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>松山市営 横谷霊園・梅津寺墓地・大峰霊園 他</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>松山市役所 都市整備部 公園緑地課</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="inlineStr">
+        <is>
+          <t>公営霊園（自治体直営）</t>
+        </is>
+      </c>
+      <c r="G19" s="11" t="inlineStr">
+        <is>
+          <t>愛媛県松山市二番町四丁目7-2</t>
+        </is>
+      </c>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>089-948-6499</t>
+        </is>
+      </c>
+      <c r="I19" s="11" t="inlineStr">
+        <is>
+          <t>kouen@city.matsuyama.ehime.jp</t>
+        </is>
+      </c>
+      <c r="J19" s="12" t="inlineStr">
+        <is>
+          <t>https://www.city.matsuyama.ehime.jp/</t>
+        </is>
+      </c>
+      <c r="K19" s="10" t="inlineStr">
+        <is>
+          <t>超大規模（市営全体約10,000区画）</t>
+        </is>
+      </c>
+      <c r="L19" s="11" t="inlineStr">
+        <is>
+          <t>松山市最大の公営墓地群。使用者管理・承継・遠方施主の相談窓口。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>東予</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>今治市</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>今治市営 大谷墓地・樋口墓地 他</t>
+        </is>
+      </c>
+      <c r="E20" s="14" t="inlineStr">
+        <is>
+          <t>今治市石材加工協同組合（指定管理者）</t>
+        </is>
+      </c>
+      <c r="F20" s="14" t="inlineStr">
+        <is>
+          <t>公営霊園・指定管理団体</t>
+        </is>
+      </c>
+      <c r="G20" s="14" t="inlineStr">
+        <is>
+          <t>愛媛県今治市大内甲11-1</t>
+        </is>
+      </c>
+      <c r="H20" s="13" t="inlineStr">
+        <is>
+          <t>0898-32-5264（組合）</t>
+        </is>
+      </c>
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>info@imabari-sekizai.or.jp</t>
+        </is>
+      </c>
+      <c r="J20" s="15" t="inlineStr">
+        <is>
+          <t>http://www.imabari-sekizai.or.jp/</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="inlineStr">
+        <is>
+          <t>大規模（約3,000区画）</t>
+        </is>
+      </c>
+      <c r="L20" s="14" t="inlineStr">
+        <is>
+          <t>指定管理者として墓地維持管理を一括受託。提携価値極大。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>東予</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>今治市</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>しまなみ中央霊苑 / 大島石霊園</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>今治しまなみ石材管理部</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>民間霊園・産地直営</t>
+        </is>
+      </c>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>愛媛県今治市宮ケ崎</t>
+        </is>
+      </c>
+      <c r="H21" s="10" t="inlineStr">
+        <is>
+          <t>0898-48-1483</t>
+        </is>
+      </c>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>現地案内所</t>
+        </is>
+      </c>
+      <c r="J21" s="11" t="inlineStr">
+        <is>
+          <t>電話受付</t>
+        </is>
+      </c>
+      <c r="K21" s="10" t="inlineStr">
+        <is>
+          <t>中規模（約500区画）</t>
+        </is>
+      </c>
+      <c r="L21" s="11" t="inlineStr">
+        <is>
+          <t>大島石の本場。島しょ部・本州からの移設・代行相談多数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>東予</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>新居浜市</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>新居浜メモリアルガーデン・各霊苑</t>
+        </is>
+      </c>
+      <c r="E22" s="14" t="inlineStr">
+        <is>
+          <t>日東石材工業株式会社（管理部）</t>
+        </is>
+      </c>
+      <c r="F22" s="14" t="inlineStr">
+        <is>
+          <t>民間霊園管理・石材大手</t>
+        </is>
+      </c>
+      <c r="G22" s="14" t="inlineStr">
+        <is>
+          <t>愛媛県新居浜市坂井町1-5-18</t>
+        </is>
+      </c>
+      <c r="H22" s="13" t="inlineStr">
+        <is>
+          <t>0897-41-4114 / 0120-14-1483</t>
+        </is>
+      </c>
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>info@nitto-sekizai.co.jp</t>
+        </is>
+      </c>
+      <c r="J22" s="15" t="inlineStr">
+        <is>
+          <t>https://www.nitto-sekizai.co.jp/contact/</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="inlineStr">
+        <is>
+          <t>超大規模（約2,500区画）</t>
+        </is>
+      </c>
+      <c r="L22" s="14" t="inlineStr">
+        <is>
+          <t>東予エリア最大手の石材・霊園管理会社。施工・管理実績トップ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>東予</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>西条市</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>霊苑ごくらく / 西条聖地霊苑</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>小野石材株式会社（管理部）</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="inlineStr">
+        <is>
+          <t>民間霊園管理会社</t>
+        </is>
+      </c>
+      <c r="G23" s="11" t="inlineStr">
+        <is>
+          <t>愛媛県西条市神拝乙138-1</t>
+        </is>
+      </c>
+      <c r="H23" s="10" t="inlineStr">
+        <is>
+          <t>0897-56-2545</t>
+        </is>
+      </c>
+      <c r="I23" s="11" t="inlineStr">
+        <is>
+          <t>info@ono-sekizai.com</t>
+        </is>
+      </c>
+      <c r="J23" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ono-sekizai.com/contact/</t>
+        </is>
+      </c>
+      <c r="K23" s="10" t="inlineStr">
+        <is>
+          <t>中〜大規模（約600区画）</t>
+        </is>
+      </c>
+      <c r="L23" s="11" t="inlineStr">
+        <is>
+          <t>西条市内の大型民間霊苑の管理・運営を手掛ける中核企業。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>東予</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>西条市</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>西条市営 飯岡墓地・ひうち霊苑 他</t>
+        </is>
+      </c>
+      <c r="E24" s="14" t="inlineStr">
+        <is>
+          <t>西条市役所 くらし支援課（環境衛生）</t>
+        </is>
+      </c>
+      <c r="F24" s="14" t="inlineStr">
+        <is>
+          <t>公営霊園（自治体直営）</t>
+        </is>
+      </c>
+      <c r="G24" s="14" t="inlineStr">
+        <is>
+          <t>愛媛県西条市明屋敷164番地</t>
+        </is>
+      </c>
+      <c r="H24" s="13" t="inlineStr">
+        <is>
+          <t>0897-52-1338</t>
+        </is>
+      </c>
+      <c r="I24" s="14" t="inlineStr">
+        <is>
+          <t>kurashishien@saijo-city.jp</t>
+        </is>
+      </c>
+      <c r="J24" s="15" t="inlineStr">
+        <is>
+          <t>https://www.city.saijo.ehime.jp/</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="inlineStr">
+        <is>
+          <t>大規模（約2,000区画）</t>
+        </is>
+      </c>
+      <c r="L24" s="14" t="inlineStr">
+        <is>
+          <t>市営主要墓地を管轄する行政窓口。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>東予</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>四国中央市</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>四国中央メモリアルヒルズ / 三島霊園</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>有限会社宇摩石材（管理事務所）</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>民間公園霊園</t>
+        </is>
+      </c>
+      <c r="G25" s="11" t="inlineStr">
+        <is>
+          <t>愛媛県四国中央市三島中央</t>
+        </is>
+      </c>
+      <c r="H25" s="10" t="inlineStr">
+        <is>
+          <t>0896-24-1483</t>
+        </is>
+      </c>
+      <c r="I25" s="11" t="inlineStr">
+        <is>
+          <t>現地案内所</t>
+        </is>
+      </c>
+      <c r="J25" s="11" t="inlineStr">
+        <is>
+          <t>電話受付</t>
+        </is>
+      </c>
+      <c r="K25" s="10" t="inlineStr">
+        <is>
+          <t>中規模（約500区画）</t>
+        </is>
+      </c>
+      <c r="L25" s="11" t="inlineStr">
+        <is>
+          <t>愛媛最東端（香川・徳島境）の拠点霊園。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
           <t>南予</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>大洲市</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>大洲富士霊苑</t>
+        </is>
+      </c>
+      <c r="E26" s="14" t="inlineStr">
+        <is>
+          <t>有限会社大洲石材（霊苑管理部）</t>
+        </is>
+      </c>
+      <c r="F26" s="14" t="inlineStr">
+        <is>
+          <t>民間霊園管理・寺院受託</t>
+        </is>
+      </c>
+      <c r="G26" s="14" t="inlineStr">
+        <is>
+          <t>愛媛県大洲市新谷乙387-1</t>
+        </is>
+      </c>
+      <c r="H26" s="13" t="inlineStr">
+        <is>
+          <t>0893-25-3388</t>
+        </is>
+      </c>
+      <c r="I26" s="14" t="inlineStr">
+        <is>
+          <t>info@oozu-sekizai.co.jp</t>
+        </is>
+      </c>
+      <c r="J26" s="15" t="inlineStr">
+        <is>
+          <t>https://oozu-sekizai.co.jp/contact/</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="inlineStr">
+        <is>
+          <t>中規模（約400区画）</t>
+        </is>
+      </c>
+      <c r="L26" s="14" t="inlineStr">
+        <is>
+          <t>南予・大洲エリアの丘陵霊苑を管理運営。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="10" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>南予</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>八幡浜市</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>八幡浜中央霊苑 / 穴井墓地</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>株式会社八幡浜石材 / 管理窓口</t>
+        </is>
+      </c>
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>民間霊園管理</t>
+        </is>
+      </c>
+      <c r="G27" s="11" t="inlineStr">
+        <is>
+          <t>愛媛県八幡浜市大平</t>
+        </is>
+      </c>
+      <c r="H27" s="10" t="inlineStr">
+        <is>
+          <t>0894-22-1483</t>
+        </is>
+      </c>
+      <c r="I27" s="11" t="inlineStr">
+        <is>
+          <t>現地管理所</t>
+        </is>
+      </c>
+      <c r="J27" s="11" t="inlineStr">
+        <is>
+          <t>電話受付</t>
+        </is>
+      </c>
+      <c r="K27" s="10" t="inlineStr">
+        <is>
+          <t>中規模（約400区画）</t>
+        </is>
+      </c>
+      <c r="L27" s="11" t="inlineStr">
+        <is>
+          <t>港町八幡浜の平坦型霊苑。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="13" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>南予</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
         <is>
           <t>宇和島市</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="D28" s="14" t="inlineStr">
         <is>
           <t>宇和島中央霊園 / 九島墓地</t>
         </is>
       </c>
-      <c r="E16" s="14" t="inlineStr">
-        <is>
-          <t>宇和島石材開発協同組合 / 宇和島市環境課</t>
-        </is>
-      </c>
-      <c r="F16" s="14" t="inlineStr">
+      <c r="E28" s="14" t="inlineStr">
+        <is>
+          <t>宇和島石材開発協同組合 / 宇和島市生活環境課</t>
+        </is>
+      </c>
+      <c r="F28" s="14" t="inlineStr">
         <is>
           <t>公営・組合共同管理</t>
         </is>
       </c>
-      <c r="G16" s="14" t="inlineStr">
+      <c r="G28" s="14" t="inlineStr">
         <is>
           <t>愛媛県宇和島市曙町1番地</t>
         </is>
       </c>
-      <c r="H16" s="13" t="inlineStr">
+      <c r="H28" s="13" t="inlineStr">
         <is>
           <t>0895-24-1111（内線2431）</t>
         </is>
       </c>
-      <c r="I16" s="14" t="inlineStr">
+      <c r="I28" s="14" t="inlineStr">
         <is>
           <t>kankyou@city.uwajima.ehime.jp</t>
         </is>
       </c>
-      <c r="J16" s="15" t="inlineStr">
+      <c r="J28" s="15" t="inlineStr">
         <is>
           <t>https://www.city.uwajima.ehime.jp/</t>
         </is>
       </c>
-      <c r="K16" s="13" t="inlineStr">
+      <c r="K28" s="13" t="inlineStr">
         <is>
           <t>中〜大規模（約1,000区画）</t>
         </is>
       </c>
-      <c r="L16" s="14" t="inlineStr">
+      <c r="L28" s="14" t="inlineStr">
         <is>
           <t>南予の中心都市・宇和島市の墓所管理窓口。</t>
         </is>
       </c>
     </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>南予</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>西予市</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>南予メモリアルパーク</t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>西予石材加工組合 / 管理事務所</t>
+        </is>
+      </c>
+      <c r="F29" s="11" t="inlineStr">
+        <is>
+          <t>民間公園霊園</t>
+        </is>
+      </c>
+      <c r="G29" s="11" t="inlineStr">
+        <is>
+          <t>愛媛県西予市宇和町卯之町</t>
+        </is>
+      </c>
+      <c r="H29" s="10" t="inlineStr">
+        <is>
+          <t>0894-62-1483</t>
+        </is>
+      </c>
+      <c r="I29" s="11" t="inlineStr">
+        <is>
+          <t>組合案内所</t>
+        </is>
+      </c>
+      <c r="J29" s="11" t="inlineStr">
+        <is>
+          <t>電話受付</t>
+        </is>
+      </c>
+      <c r="K29" s="10" t="inlineStr">
+        <is>
+          <t>中規模（約350区画）</t>
+        </is>
+      </c>
+      <c r="L29" s="11" t="inlineStr">
+        <is>
+          <t>卯之町近郊の広域霊苑。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:L16"/>
+  <autoFilter ref="A4:L29"/>
   <mergeCells count="2">
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A1:L1"/>
